--- a/data/file_generation/input/data_200/彩票形态分析Excel_优化版.xlsx
+++ b/data/file_generation/input/data_200/彩票形态分析Excel_优化版.xlsx
@@ -2702,18 +2702,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{184D1780-9A72-4B59-9717-7ACB2D715B41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F95E3C5D-541B-4FF6-BB70-DA013A8B61B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BA7525A-2FF9-444B-B167-107864B89538}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B9CCBA-0B7B-4EF6-946E-97FC0162A526}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E9AC0A7-8F64-4C54-82C3-2A0DD7D8FEB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{994601B1-37B6-46A3-9CD2-10EBFEC35395}"/>
 </file>